--- a/static/data/database/JSS3_Students.xlsx
+++ b/static/data/database/JSS3_Students.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JSS3 Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'JSS3 Students'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'JSS3 Students'!$A$1:$H$75</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -470,8 +470,2976 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>std160</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AZEEM</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ADETUNJI</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>08136162408</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>JSS3A</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>std161</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ABDUL</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>UMAR</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ALECHENZI</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>07069593719</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>JSS3A</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>std162</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ABDULHAFIZ</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AMINU</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>08035976838</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>JSS3A</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>std163</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>AISHA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>IBRAHIM</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ABDULLAHI</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>08031579478</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>JSS3A</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>std164</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ALHASSAN</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>MUHAMMAD</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>SULAIMAN</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>08033310111</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>JSS3A</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>std165</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>AMIRA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>RAJI</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>08067444552</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>JSS3A</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>std166</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ABUSALMA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>IBRAHIM</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>07066774164</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>JSS3A</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>std167</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ABDULAZEEZ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>IBRAHIM</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>08057727924</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>JSS3A</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>std168</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>FATIMA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ZARAH</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>JIBRIL</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>08036668605</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>JSS3A</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>std169</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>FIRDAUSI</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>KASHEM</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>07033452007</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>JSS3A</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>std170</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>HANIFAH</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ADETOYE</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>07068505744</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>JSS3A</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>std171</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>IMRAN</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>DAHIRU</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>07066666860</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>JSS3A</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>std172</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ISMA'IL</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ABDULKABIR</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>07064645550</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>JSS3A</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>std173</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>KAMILAH</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>RAJI</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>080334971256</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>JSS3A</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>std174</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>KHADIJA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>YERIMA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>08162354054</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>JSS3A</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>std175</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>MAHMUD</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>KABIRU</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>MUKTAR</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>08035112956</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>JSS3A</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>std176</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>MUHSINA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>BELLO</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>07038251084</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>JSS3A</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>std177</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>MUHAMMAD</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SAMIR</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ZAIYANU</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>07030927742</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>JSS3A</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>std178</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>NA'IMA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AUWAL</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>IBRAHIM</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>08033371313</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>JSS3A</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>std179</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>NANA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AUWAL</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ABDULHAKEEM</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>08036544182</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>JSS3A</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>std180</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>RAJI</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>TUKUR</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>KAWU</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>07061800414</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>JSS3A</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>std181</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>RUTH</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EZE</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>08063155872</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>JSS3A</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>std182</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>RUKKAIYA</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ABAMAMMAN</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>08036134213</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>JSS3A</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>std183</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>YUSRA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ABDULRASHEED</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>08023797649</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>JSS3A</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>std184</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ZAINAB</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ALIYU</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>09186644664</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>JSS3A</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>std185</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ZAKIYYAH</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>IBRAHIM</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>OMONYE</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>08035290331</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>JSS3A</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>std186</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>KHADIJA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>MUHAMMAD</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>09164925212</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>JSS3A</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>std187</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>MUSA</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>YUSUF</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>UMAR</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>07031940146</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>JSS3B</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>std188</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ADAMU</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>YAKUBU</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>09022340559</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>JSS3B</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>std189</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>MOHAMMAD</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NASIR</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>07064493655</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>JSS3B</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>std190</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>AHMAD</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>MUHAMMAD</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AFFAN</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>08068694226</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>JSS3B</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>std191</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ABDUL-QADIR</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>KHALIFA</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>KABIR</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>08034800600</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>JSS3B</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>std192</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>IBRAHIM</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ABDULWAHAB</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>08077229624</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>JSS3B</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>std193</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>USMAN</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ADAMU</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>ISHAQ</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>08131449884</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>JSS3B</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>std194</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>IRFAN</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>FARUK</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>IDIARO</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>08033707456</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>JSS3B</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>std195</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>OMALE</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>JORDAN</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>08073173763</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>JSS3B</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>std196</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>UMMULKULTHUM</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>HAYATU</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>WAZIRI</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>08026329671</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>JSS3B</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>std197</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>MUHAMMED</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>HAUWA</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>08033697673</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>JSS3B</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>std198</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>SUMIA</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>MOMOD</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>07064174881</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>JSS3B</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>std199</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>IDRIS</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>MARYAM</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>RABIU</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>08036077039</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>JSS3B</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>std200</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ABBAKURA</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>FATIMAH</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>ALI</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>08032167508</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>JSS3B</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>std201</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ISMAIL</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>LAMIA</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>07063619332</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>JSS3B</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>std202</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>IDOWU</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>NIMATULLAHI</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>A.</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>08036888250</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>JSS3B</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>std203</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>SUNUSI</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>AMIR</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>08166677184</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>JSS3B</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>std204</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ISMAIL</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>UMMU</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>SHURAIHA</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>08032892838</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>JSS3B</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>std205</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>UTHMAN</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>MUHAMMAD</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>JAWAD</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>08065474565</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>JSS3B</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>std206</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>MUKHTAR</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>AISHA</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>AHMAD</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>08139191130</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>JSS3B</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>std207</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>OLOPADE</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>ABDUL</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>WARIS</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>08165453077</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>JSS3B</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>std208</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>ABDULLAHI</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>IDRIS</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>ABDULLAHI</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>08093871791</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>JSS3B</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>std209</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>ABBAKURA</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>FATIMA</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>ZAHRA</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>08032109299</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>JSS3C</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>std210</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>FATIMA</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ABDULJABBAR</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>08027950448</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>JSS3C</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>std211</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>AISHA</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>ABUBAKAR</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>GIREI</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>08036232351</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>JSS3C</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>std212</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>YUSRAH</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>IBRAHIM</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>A.</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>08062602000</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>JSS3C</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>std213</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>RAMLA</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>YAHAYA</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>YAKUBU</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>08064607626</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>JSS3C</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>std214</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>SAFEEYAH</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>MUHAMMAD</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>H.</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>08028398915</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>JSS3C</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>std215</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>UMMULKHAIR</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ZUBAIRU</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>08035952585</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>JSS3C</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>std216</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>FAIZA</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>MUDARRIFU</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>F.</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>08015404681</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>JSS3C</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>std217</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>AISHA</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>POPOOLA</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>IREBAMI</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>07022766863</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>JSS3C</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>std218</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>HAFSAT</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>A.</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>MUHAMMAD</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>08003805010</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>JSS3C</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>std219</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>RAYYANNA</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ALLI</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>ADEJOUN</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>07067020234</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>JSS3C</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>std220</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>SAFEEYAH</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>SAEED</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>YAHAYA</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>08033110134</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>JSS3C</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>std221</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>ABDULGANIYU</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>AUDU</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>08023323811</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>JSS3C</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>std222</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>ZAYYAN</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>ZAYYAN</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>07068800574</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>JSS3C</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>std223</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>ABUBAKAR</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>AUWAL</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>BELLO</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>08034948449</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>JSS3C</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>std224</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>MURTALA</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>HALIRU</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>AMBURSA</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>08068067508</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>JSS3C</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>std225</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>YAHAYA</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>HABUFARI</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>08099944553</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>JSS3C</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>std226</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>BAWA</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>MAHMUD</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>07068816607</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>JSS3C</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>std227</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>FARHAN</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>MUHAMMAD</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>08036422227</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>JSS3C</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>std228</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>ABBAS</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>ABBAS</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>BELLO</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>07034448544</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>JSS3C</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>std229</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>SANI</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>MUHAMMAD</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>08030733215</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>JSS3C</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>std230</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>SALISU</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>YUSUF</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>BAYERO</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>08199944444</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>JSS3C</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>std231</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>SALIHU</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>ABUBAKAR</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>08035839220</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>JSS3C</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>std232</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>ABDULHAMID</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>IBRAHIM</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>08072229644</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>JSS3C</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>std233</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>ABDULLAHI</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>DANMALAM</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>09090424235</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>JSS3C</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>JSS3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H1"/>
+  <autoFilter ref="A1:H75"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>